--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -1076,32 +1076,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127753097</v>
+        <v>127753091</v>
       </c>
       <c r="B6" t="n">
-        <v>91493</v>
+        <v>91282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>757850</v>
+        <v>757780</v>
       </c>
       <c r="R6" t="n">
-        <v>7227196</v>
+        <v>7226987</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,32 +1173,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753091</v>
+        <v>127753097</v>
       </c>
       <c r="B7" t="n">
-        <v>91282</v>
+        <v>91493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>757780</v>
+        <v>757850</v>
       </c>
       <c r="R7" t="n">
-        <v>7226987</v>
+        <v>7227196</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753087</v>
+        <v>127753096</v>
       </c>
       <c r="B8" t="n">
-        <v>56855</v>
+        <v>97333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,42 +1281,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>757846</v>
+        <v>757896</v>
       </c>
       <c r="R8" t="n">
-        <v>7227288</v>
+        <v>7227173</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1349,11 +1341,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753096</v>
+        <v>127753087</v>
       </c>
       <c r="B9" t="n">
-        <v>97333</v>
+        <v>56855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,34 +1378,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>757896</v>
+        <v>757846</v>
       </c>
       <c r="R9" t="n">
-        <v>7227173</v>
+        <v>7227288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,6 +1446,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92616</v>
+        <v>92622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86785</v>
+        <v>86787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,32 +1076,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127753091</v>
+        <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91282</v>
+        <v>91499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>757780</v>
+        <v>757850</v>
       </c>
       <c r="R6" t="n">
-        <v>7226987</v>
+        <v>7227196</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,32 +1173,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753097</v>
+        <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91493</v>
+        <v>91288</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>757850</v>
+        <v>757780</v>
       </c>
       <c r="R7" t="n">
-        <v>7227196</v>
+        <v>7226987</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753096</v>
+        <v>127753087</v>
       </c>
       <c r="B8" t="n">
-        <v>97333</v>
+        <v>56855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,34 +1281,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>757896</v>
+        <v>757846</v>
       </c>
       <c r="R8" t="n">
-        <v>7227173</v>
+        <v>7227288</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1341,6 +1349,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753087</v>
+        <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>56855</v>
+        <v>97339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,42 +1391,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>757846</v>
+        <v>757896</v>
       </c>
       <c r="R9" t="n">
-        <v>7227288</v>
+        <v>7227173</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1446,11 +1451,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1480,7 +1480,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92616</v>
+        <v>92622</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,53 +1870,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753088</v>
+        <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>92632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>757723</v>
+        <v>757850</v>
       </c>
       <c r="R14" t="n">
-        <v>7227050</v>
+        <v>7227196</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,45 +1967,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753094</v>
+        <v>127753088</v>
       </c>
       <c r="B15" t="n">
-        <v>92626</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>757850</v>
+        <v>757723</v>
       </c>
       <c r="R15" t="n">
-        <v>7227196</v>
+        <v>7227050</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,7 +2075,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92622</v>
+        <v>92625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753086</v>
+        <v>127753093</v>
       </c>
       <c r="B3" t="n">
-        <v>86787</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3690</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>757959</v>
+        <v>757735</v>
       </c>
       <c r="R3" t="n">
-        <v>7227207</v>
+        <v>7227098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753093</v>
+        <v>127753086</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>86790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +893,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>3690</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757735</v>
+        <v>757959</v>
       </c>
       <c r="R4" t="n">
-        <v>7227098</v>
+        <v>7227207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +953,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,7 +982,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,32 +1076,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127753097</v>
+        <v>127753091</v>
       </c>
       <c r="B6" t="n">
-        <v>91499</v>
+        <v>91291</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>757850</v>
+        <v>757780</v>
       </c>
       <c r="R6" t="n">
-        <v>7227196</v>
+        <v>7226987</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,32 +1173,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753091</v>
+        <v>127753097</v>
       </c>
       <c r="B7" t="n">
-        <v>91288</v>
+        <v>91502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>757780</v>
+        <v>757850</v>
       </c>
       <c r="R7" t="n">
-        <v>7226987</v>
+        <v>7227196</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,7 +1273,7 @@
         <v>127753087</v>
       </c>
       <c r="B8" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753098</v>
+        <v>127753095</v>
       </c>
       <c r="B10" t="n">
-        <v>92628</v>
+        <v>97342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>757852</v>
+        <v>757964</v>
       </c>
       <c r="R10" t="n">
-        <v>7227223</v>
+        <v>7227206</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753095</v>
+        <v>127753098</v>
       </c>
       <c r="B11" t="n">
-        <v>97339</v>
+        <v>92631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,21 +1585,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>757964</v>
+        <v>757852</v>
       </c>
       <c r="R11" t="n">
-        <v>7227206</v>
+        <v>7227223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92622</v>
+        <v>92625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92632</v>
+        <v>92635</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>127753088</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753093</v>
+        <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>86796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>3690</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>757735</v>
+        <v>757959</v>
       </c>
       <c r="R3" t="n">
-        <v>7227098</v>
+        <v>7227207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753086</v>
+        <v>127753093</v>
       </c>
       <c r="B4" t="n">
-        <v>86790</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3690</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757959</v>
+        <v>757735</v>
       </c>
       <c r="R4" t="n">
-        <v>7227207</v>
+        <v>7227098</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,7 +982,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127753091</v>
       </c>
       <c r="B6" t="n">
-        <v>91291</v>
+        <v>91299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127753097</v>
       </c>
       <c r="B7" t="n">
-        <v>91502</v>
+        <v>91510</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753087</v>
+        <v>127753096</v>
       </c>
       <c r="B8" t="n">
-        <v>56858</v>
+        <v>97350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,42 +1281,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>757846</v>
+        <v>757896</v>
       </c>
       <c r="R8" t="n">
-        <v>7227288</v>
+        <v>7227173</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1349,11 +1341,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753096</v>
+        <v>127753087</v>
       </c>
       <c r="B9" t="n">
-        <v>97342</v>
+        <v>56864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,34 +1378,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>757896</v>
+        <v>757846</v>
       </c>
       <c r="R9" t="n">
-        <v>7227173</v>
+        <v>7227288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,6 +1446,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1477,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753095</v>
+        <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>97342</v>
+        <v>92639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>757964</v>
+        <v>757852</v>
       </c>
       <c r="R10" t="n">
-        <v>7227206</v>
+        <v>7227223</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753098</v>
+        <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>92631</v>
+        <v>97350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,21 +1585,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>757852</v>
+        <v>757964</v>
       </c>
       <c r="R11" t="n">
-        <v>7227223</v>
+        <v>7227206</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,45 +1870,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753094</v>
+        <v>127753088</v>
       </c>
       <c r="B14" t="n">
-        <v>92635</v>
+        <v>57832</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>757850</v>
+        <v>757723</v>
       </c>
       <c r="R14" t="n">
-        <v>7227196</v>
+        <v>7227050</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1967,53 +1975,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753088</v>
+        <v>127753094</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>92643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>757723</v>
+        <v>757850</v>
       </c>
       <c r="R15" t="n">
-        <v>7227050</v>
+        <v>7227196</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,7 +2075,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127753091</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>91300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127753097</v>
       </c>
       <c r="B7" t="n">
-        <v>91510</v>
+        <v>91511</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127753096</v>
       </c>
       <c r="B8" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753098</v>
+        <v>127753095</v>
       </c>
       <c r="B10" t="n">
-        <v>92639</v>
+        <v>97351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>757852</v>
+        <v>757964</v>
       </c>
       <c r="R10" t="n">
-        <v>7227223</v>
+        <v>7227206</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753095</v>
+        <v>127753098</v>
       </c>
       <c r="B11" t="n">
-        <v>97350</v>
+        <v>92640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,21 +1585,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>757964</v>
+        <v>757852</v>
       </c>
       <c r="R11" t="n">
-        <v>7227206</v>
+        <v>7227223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,53 +1870,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753088</v>
+        <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>57832</v>
+        <v>92644</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>757723</v>
+        <v>757850</v>
       </c>
       <c r="R14" t="n">
-        <v>7227050</v>
+        <v>7227196</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,45 +1967,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753094</v>
+        <v>127753088</v>
       </c>
       <c r="B15" t="n">
-        <v>92643</v>
+        <v>57832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>757850</v>
+        <v>757723</v>
       </c>
       <c r="R15" t="n">
-        <v>7227196</v>
+        <v>7227050</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,7 +2075,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -1477,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753095</v>
+        <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>97351</v>
+        <v>92640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>757964</v>
+        <v>757852</v>
       </c>
       <c r="R10" t="n">
-        <v>7227206</v>
+        <v>7227223</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753098</v>
+        <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>92640</v>
+        <v>97351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,21 +1585,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>757852</v>
+        <v>757964</v>
       </c>
       <c r="R11" t="n">
-        <v>7227223</v>
+        <v>7227206</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86796</v>
+        <v>86797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127753091</v>
       </c>
       <c r="B6" t="n">
-        <v>91300</v>
+        <v>91301</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127753097</v>
       </c>
       <c r="B7" t="n">
-        <v>91511</v>
+        <v>91512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753096</v>
+        <v>127753087</v>
       </c>
       <c r="B8" t="n">
-        <v>97351</v>
+        <v>56864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,34 +1281,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>757896</v>
+        <v>757846</v>
       </c>
       <c r="R8" t="n">
-        <v>7227173</v>
+        <v>7227288</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1341,6 +1349,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753087</v>
+        <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>56864</v>
+        <v>97352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,42 +1391,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>757846</v>
+        <v>757896</v>
       </c>
       <c r="R9" t="n">
-        <v>7227288</v>
+        <v>7227173</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1446,11 +1451,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1480,7 +1480,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97351</v>
+        <v>97352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92644</v>
+        <v>92645</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753086</v>
+        <v>127753093</v>
       </c>
       <c r="B3" t="n">
-        <v>86797</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3690</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>757959</v>
+        <v>757735</v>
       </c>
       <c r="R3" t="n">
-        <v>7227207</v>
+        <v>7227098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753093</v>
+        <v>127753086</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>86798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +893,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>3690</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757735</v>
+        <v>757959</v>
       </c>
       <c r="R4" t="n">
-        <v>7227098</v>
+        <v>7227207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +953,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,7 +982,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,32 +1076,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127753091</v>
+        <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91301</v>
+        <v>91513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>757780</v>
+        <v>757850</v>
       </c>
       <c r="R6" t="n">
-        <v>7226987</v>
+        <v>7227196</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,32 +1173,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753097</v>
+        <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91512</v>
+        <v>91302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>757850</v>
+        <v>757780</v>
       </c>
       <c r="R7" t="n">
-        <v>7227196</v>
+        <v>7226987</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753087</v>
+        <v>127753096</v>
       </c>
       <c r="B8" t="n">
-        <v>56864</v>
+        <v>97353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,42 +1281,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>757846</v>
+        <v>757896</v>
       </c>
       <c r="R8" t="n">
-        <v>7227288</v>
+        <v>7227173</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1349,11 +1341,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753096</v>
+        <v>127753087</v>
       </c>
       <c r="B9" t="n">
-        <v>97352</v>
+        <v>56864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,34 +1378,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>757896</v>
+        <v>757846</v>
       </c>
       <c r="R9" t="n">
-        <v>7227173</v>
+        <v>7227288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,6 +1446,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1480,7 +1480,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92645</v>
+        <v>92646</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -1076,32 +1076,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127753097</v>
+        <v>127753091</v>
       </c>
       <c r="B6" t="n">
-        <v>91513</v>
+        <v>91302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>757850</v>
+        <v>757780</v>
       </c>
       <c r="R6" t="n">
-        <v>7227196</v>
+        <v>7226987</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,32 +1173,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753091</v>
+        <v>127753097</v>
       </c>
       <c r="B7" t="n">
-        <v>91302</v>
+        <v>91513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>757780</v>
+        <v>757850</v>
       </c>
       <c r="R7" t="n">
-        <v>7226987</v>
+        <v>7227196</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753096</v>
+        <v>127753087</v>
       </c>
       <c r="B8" t="n">
-        <v>97353</v>
+        <v>56864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,34 +1281,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>757896</v>
+        <v>757846</v>
       </c>
       <c r="R8" t="n">
-        <v>7227173</v>
+        <v>7227288</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1341,6 +1349,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753087</v>
+        <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>56864</v>
+        <v>97353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,42 +1391,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>757846</v>
+        <v>757896</v>
       </c>
       <c r="R9" t="n">
-        <v>7227288</v>
+        <v>7227173</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1446,11 +1451,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1477,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753098</v>
+        <v>127753095</v>
       </c>
       <c r="B10" t="n">
-        <v>92642</v>
+        <v>97353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>757852</v>
+        <v>757964</v>
       </c>
       <c r="R10" t="n">
-        <v>7227223</v>
+        <v>7227206</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753095</v>
+        <v>127753098</v>
       </c>
       <c r="B11" t="n">
-        <v>97353</v>
+        <v>92642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,21 +1585,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>757964</v>
+        <v>757852</v>
       </c>
       <c r="R11" t="n">
-        <v>7227206</v>
+        <v>7227223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753093</v>
+        <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>86798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>3690</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>757735</v>
+        <v>757959</v>
       </c>
       <c r="R3" t="n">
-        <v>7227098</v>
+        <v>7227207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753086</v>
+        <v>127753093</v>
       </c>
       <c r="B4" t="n">
-        <v>86798</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3690</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757959</v>
+        <v>757735</v>
       </c>
       <c r="R4" t="n">
-        <v>7227207</v>
+        <v>7227098</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753086</v>
+        <v>127753093</v>
       </c>
       <c r="B3" t="n">
-        <v>86798</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3690</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>757959</v>
+        <v>757735</v>
       </c>
       <c r="R3" t="n">
-        <v>7227207</v>
+        <v>7227098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753093</v>
+        <v>127753086</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>86798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +893,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>3690</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757735</v>
+        <v>757959</v>
       </c>
       <c r="R4" t="n">
-        <v>7227098</v>
+        <v>7227207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +953,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753093</v>
+        <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>86802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>3690</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>757735</v>
+        <v>757959</v>
       </c>
       <c r="R3" t="n">
-        <v>7227098</v>
+        <v>7227207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753086</v>
+        <v>127753093</v>
       </c>
       <c r="B4" t="n">
-        <v>86798</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3690</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757959</v>
+        <v>757735</v>
       </c>
       <c r="R4" t="n">
-        <v>7227207</v>
+        <v>7227098</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,7 +982,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127753091</v>
       </c>
       <c r="B6" t="n">
-        <v>91302</v>
+        <v>91310</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127753097</v>
       </c>
       <c r="B7" t="n">
-        <v>91513</v>
+        <v>91521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753087</v>
+        <v>127753096</v>
       </c>
       <c r="B8" t="n">
-        <v>56864</v>
+        <v>97361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,42 +1281,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>757846</v>
+        <v>757896</v>
       </c>
       <c r="R8" t="n">
-        <v>7227288</v>
+        <v>7227173</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1349,11 +1341,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753096</v>
+        <v>127753087</v>
       </c>
       <c r="B9" t="n">
-        <v>97353</v>
+        <v>56864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,34 +1378,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>757896</v>
+        <v>757846</v>
       </c>
       <c r="R9" t="n">
-        <v>7227173</v>
+        <v>7227288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,6 +1446,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1480,7 +1480,7 @@
         <v>127753095</v>
       </c>
       <c r="B10" t="n">
-        <v>97353</v>
+        <v>97361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>127753098</v>
       </c>
       <c r="B11" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92646</v>
+        <v>92654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>127753088</v>
       </c>
       <c r="B15" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -1870,45 +1870,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753094</v>
+        <v>127753088</v>
       </c>
       <c r="B14" t="n">
-        <v>92654</v>
+        <v>57833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>757850</v>
+        <v>757723</v>
       </c>
       <c r="R14" t="n">
-        <v>7227196</v>
+        <v>7227050</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1967,53 +1975,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753088</v>
+        <v>127753094</v>
       </c>
       <c r="B15" t="n">
-        <v>57833</v>
+        <v>92654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>757723</v>
+        <v>757850</v>
       </c>
       <c r="R15" t="n">
-        <v>7227050</v>
+        <v>7227196</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86802</v>
+        <v>86894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127753093</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,32 +1076,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127753091</v>
+        <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91310</v>
+        <v>91613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>757780</v>
+        <v>757850</v>
       </c>
       <c r="R6" t="n">
-        <v>7226987</v>
+        <v>7227196</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,32 +1173,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753097</v>
+        <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91521</v>
+        <v>91402</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>757850</v>
+        <v>757780</v>
       </c>
       <c r="R7" t="n">
-        <v>7227196</v>
+        <v>7226987</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753096</v>
+        <v>127753087</v>
       </c>
       <c r="B8" t="n">
-        <v>97361</v>
+        <v>56876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,34 +1281,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>757896</v>
+        <v>757846</v>
       </c>
       <c r="R8" t="n">
-        <v>7227173</v>
+        <v>7227288</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1341,6 +1349,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753087</v>
+        <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>56864</v>
+        <v>97454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,42 +1391,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>757846</v>
+        <v>757896</v>
       </c>
       <c r="R9" t="n">
-        <v>7227288</v>
+        <v>7227173</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1446,11 +1451,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1477,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753095</v>
+        <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>97361</v>
+        <v>92742</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>757964</v>
+        <v>757852</v>
       </c>
       <c r="R10" t="n">
-        <v>7227206</v>
+        <v>7227223</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753098</v>
+        <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>92650</v>
+        <v>97454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,21 +1585,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>757852</v>
+        <v>757964</v>
       </c>
       <c r="R11" t="n">
-        <v>7227223</v>
+        <v>7227206</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,53 +1870,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753088</v>
+        <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>57833</v>
+        <v>92746</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>757723</v>
+        <v>757850</v>
       </c>
       <c r="R14" t="n">
-        <v>7227050</v>
+        <v>7227196</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,45 +1967,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753094</v>
+        <v>127753088</v>
       </c>
       <c r="B15" t="n">
-        <v>92654</v>
+        <v>57845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Degerträskån, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>757850</v>
+        <v>757723</v>
       </c>
       <c r="R15" t="n">
-        <v>7227196</v>
+        <v>7227050</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,7 +2075,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92736</v>
+        <v>92788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86894</v>
+        <v>86938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127753093</v>
       </c>
       <c r="B4" t="n">
-        <v>57682</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,14 +983,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,14 +1084,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91613</v>
+        <v>91665</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,14 +1185,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91402</v>
+        <v>91454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,14 +1286,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127753087</v>
       </c>
       <c r="B8" t="n">
-        <v>56876</v>
+        <v>56907</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,14 +1400,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97454</v>
+        <v>97509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,14 +1501,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,14 +1602,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97454</v>
+        <v>97509</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,14 +1703,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,14 +1804,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92736</v>
+        <v>92788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,14 +1910,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92746</v>
+        <v>92798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1963,14 +2011,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127753088</v>
       </c>
       <c r="B15" t="n">
-        <v>57845</v>
+        <v>57876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,14 +2120,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2221,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86938</v>
+        <v>86942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753093</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91665</v>
+        <v>91669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91454</v>
+        <v>91458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>127753087</v>
       </c>
       <c r="B8" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>127753088</v>
       </c>
       <c r="B15" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86942</v>
+        <v>86947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753093</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91669</v>
+        <v>91674</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91458</v>
+        <v>91463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>127753087</v>
       </c>
       <c r="B8" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>127753088</v>
       </c>
       <c r="B15" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86954</v>
+        <v>86957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91681</v>
+        <v>91684</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91470</v>
+        <v>91473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92810</v>
+        <v>92813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86957</v>
+        <v>86960</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91684</v>
+        <v>91687</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92810</v>
+        <v>92813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86960</v>
+        <v>86964</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753093</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91687</v>
+        <v>91694</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>127753087</v>
       </c>
       <c r="B8" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>127753088</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92820</v>
+        <v>92827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86964</v>
+        <v>86971</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91694</v>
+        <v>91701</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91482</v>
+        <v>91489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92820</v>
+        <v>92827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92827</v>
+        <v>92829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86971</v>
+        <v>86973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753093</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91489</v>
+        <v>91491</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>127753087</v>
       </c>
       <c r="B8" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92827</v>
+        <v>92829</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>127753088</v>
       </c>
       <c r="B15" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92829</v>
+        <v>92815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86973</v>
+        <v>86974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91703</v>
+        <v>91712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92829</v>
+        <v>92815</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92815</v>
+        <v>92816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91712</v>
+        <v>91713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92815</v>
+        <v>92816</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -1411,7 +1411,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86974</v>
+        <v>86977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91713</v>
+        <v>91716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91491</v>
+        <v>91494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92819</v>
+        <v>92821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86977</v>
+        <v>86979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91716</v>
+        <v>91718</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91494</v>
+        <v>91496</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92819</v>
+        <v>92821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32934-2025 artfynd.xlsx
+++ b/artfynd/A 32934-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753103</v>
       </c>
       <c r="B2" t="n">
-        <v>92821</v>
+        <v>92825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753086</v>
       </c>
       <c r="B3" t="n">
-        <v>86979</v>
+        <v>86983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127753099</v>
       </c>
       <c r="B5" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>127753097</v>
       </c>
       <c r="B6" t="n">
-        <v>91718</v>
+        <v>91722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127753091</v>
       </c>
       <c r="B7" t="n">
-        <v>91496</v>
+        <v>91500</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127753096</v>
       </c>
       <c r="B9" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127753098</v>
       </c>
       <c r="B10" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>127753095</v>
       </c>
       <c r="B11" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>127753101</v>
       </c>
       <c r="B12" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>127753102</v>
       </c>
       <c r="B13" t="n">
-        <v>92821</v>
+        <v>92825</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127753094</v>
       </c>
       <c r="B14" t="n">
-        <v>92831</v>
+        <v>92835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>127753100</v>
       </c>
       <c r="B16" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
